--- a/data/trans_camb/P1435-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1435-Habitat-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,28</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,45</t>
+          <t>-2,57; 1,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -1,2</t>
+          <t>-4,48; -1,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,36</t>
+          <t>-1,97; 2,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,45</t>
+          <t>-2,57; 1,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -1,2</t>
+          <t>-4,48; -1,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,36</t>
+          <t>-1,97; 2,49</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 47,44</t>
+          <t>-50,52; 49,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,84; -27,64</t>
+          <t>-86,77; -29,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 79,32</t>
+          <t>-39,25; 80,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 47,44</t>
+          <t>-50,52; 49,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,84; -27,64</t>
+          <t>-86,77; -29,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 79,32</t>
+          <t>-39,25; 80,68</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,47</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,23</t>
+          <t>-3,49; 0,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; -2,54</t>
+          <t>-5,67; -2,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,49</t>
+          <t>-1,68; 2,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,23</t>
+          <t>-3,49; 0,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; -2,54</t>
+          <t>-5,67; -2,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,49</t>
+          <t>-1,68; 2,3</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,55; 6,53</t>
+          <t>-57,34; 11,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-90,67; -63,57</t>
+          <t>-90,37; -62,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 60,98</t>
+          <t>-26,2; 58,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-57,55; 6,53</t>
+          <t>-57,34; 11,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,67; -63,57</t>
+          <t>-90,37; -62,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 60,98</t>
+          <t>-26,2; 58,4</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,2</t>
+          <t>-3,54</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,2</t>
+          <t>-3,54</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -3,72</t>
+          <t>-9,36; -3,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,83; -7,74</t>
+          <t>-13,08; -7,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,47; -2,74</t>
+          <t>-6,29; -0,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -3,72</t>
+          <t>-9,36; -3,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,83; -7,74</t>
+          <t>-13,08; -7,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,47; -2,74</t>
+          <t>-6,29; -0,01</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-51,58%</t>
+          <t>-29,43%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-51,58%</t>
+          <t>-29,43%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,65; -35,25</t>
+          <t>-68,22; -35,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-92,77; -75,89</t>
+          <t>-92,03; -75,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,29; -27,55</t>
+          <t>-48,45; -0,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,65; -35,25</t>
+          <t>-68,22; -35,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-92,77; -75,89</t>
+          <t>-92,03; -75,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,29; -27,55</t>
+          <t>-48,45; -0,31</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>-3,49</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>-3,49</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,85; -4,32</t>
+          <t>-8,8; -4,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -4,46</t>
+          <t>-8,91; -4,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 20,52</t>
+          <t>-5,81; -1,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,85; -4,32</t>
+          <t>-8,8; -4,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -4,46</t>
+          <t>-8,91; -4,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 20,52</t>
+          <t>-5,81; -1,29</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>-35,61%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>-35,61%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-76,75; -48,8</t>
+          <t>-76,84; -49,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-77,28; -51,86</t>
+          <t>-78,79; -52,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-44,32; 234,58</t>
+          <t>-52,09; -14,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-76,75; -48,8</t>
+          <t>-76,84; -49,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-77,28; -51,86</t>
+          <t>-78,79; -52,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,32; 234,58</t>
+          <t>-52,09; -14,19</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-1,55</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-1,55</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -2,8</t>
+          <t>-4,98; -2,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -4,79</t>
+          <t>-6,88; -4,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,29</t>
+          <t>-2,74; -0,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -2,8</t>
+          <t>-4,98; -2,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -4,79</t>
+          <t>-6,88; -4,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,29</t>
+          <t>-2,74; -0,31</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-20,14%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-20,14%</t>
         </is>
       </c>
     </row>
@@ -1334,32 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-58,64; -38,93</t>
+          <t>-59,39; -39,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-81,24; -68,31</t>
+          <t>-81,64; -68,02</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 85,98</t>
+          <t>-32,82; -4,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-58,64; -38,93</t>
+          <t>-59,39; -39,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-81,24; -68,31</t>
+          <t>-81,64; -68,02</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 85,98</t>
+          <t>-32,82; -4,27</t>
         </is>
       </c>
     </row>
